--- a/results/uci__age-group__full-clinical-panel/results.xlsx
+++ b/results/uci__age-group__full-clinical-panel/results.xlsx
@@ -24,13 +24,14 @@
     <sheet name="select_picks_summary" sheetId="15" r:id="rId15"/>
     <sheet name="pareto" sheetId="16" r:id="rId16"/>
     <sheet name="shap_by_group" sheetId="17" r:id="rId17"/>
+    <sheet name="lime_shap_agreement" sheetId="18" r:id="rId18"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="327">
   <si>
     <t>Value</t>
   </si>
@@ -596,15 +597,24 @@
     <t>Reweighing (pre-processing)</t>
   </si>
   <si>
+    <t>Group-balanced SMOTE (pre-processing)</t>
+  </si>
+  <si>
     <t>Exponentiated Gradient (in-processing)</t>
   </si>
   <si>
     <t>Threshold Optimizer (post-processing)</t>
   </si>
   <si>
+    <t>Reject Option Classification (post-processing)</t>
+  </si>
+  <si>
     <t>Reweighing + Threshold Optimizer (hybrid)</t>
   </si>
   <si>
+    <t>0.994 ± 0.003</t>
+  </si>
+  <si>
     <t>0.995 ± 0.002</t>
   </si>
   <si>
@@ -614,9 +624,15 @@
     <t>0.988 ± 0.002</t>
   </si>
   <si>
+    <t>0.989 ± 0.001</t>
+  </si>
+  <si>
     <t>0.980 ± 0.007</t>
   </si>
   <si>
+    <t>0.991 ± 0.001</t>
+  </si>
+  <si>
     <t>0.977 ± 0.003</t>
   </si>
   <si>
@@ -638,6 +654,9 @@
     <t>0.980 ± 0.006</t>
   </si>
   <si>
+    <t>0.990 ± 0.001</t>
+  </si>
+  <si>
     <t>0.978 ± 0.001</t>
   </si>
   <si>
@@ -647,15 +666,24 @@
     <t>0.996 ± 0.005</t>
   </si>
   <si>
+    <t>0.991 ± 0.005</t>
+  </si>
+  <si>
     <t>0.994 ± 0.005</t>
   </si>
   <si>
     <t>0.993 ± 0.002</t>
   </si>
   <si>
+    <t>0.992 ± 0.000</t>
+  </si>
+  <si>
     <t>0.978 ± 0.013</t>
   </si>
   <si>
+    <t>0.994 ± 0.002</t>
+  </si>
+  <si>
     <t>0.975 ± 0.012</t>
   </si>
   <si>
@@ -674,9 +702,15 @@
     <t>0.269 ± 0.005</t>
   </si>
   <si>
+    <t>0.274 ± 0.005</t>
+  </si>
+  <si>
     <t>0.265 ± 0.005</t>
   </si>
   <si>
+    <t>0.268 ± 0.007</t>
+  </si>
+  <si>
     <t>0.263 ± 0.005</t>
   </si>
   <si>
@@ -689,9 +723,15 @@
     <t>0.261 ± 0.004</t>
   </si>
   <si>
+    <t>0.264 ± 0.002</t>
+  </si>
+  <si>
     <t>0.255 ± 0.019</t>
   </si>
   <si>
+    <t>0.261 ± 0.003</t>
+  </si>
+  <si>
     <t>0.254 ± 0.021</t>
   </si>
   <si>
@@ -704,9 +744,15 @@
     <t>0.656 ± 0.007</t>
   </si>
   <si>
+    <t>0.649 ± 0.006</t>
+  </si>
+  <si>
     <t>0.660 ± 0.007</t>
   </si>
   <si>
+    <t>0.657 ± 0.008</t>
+  </si>
+  <si>
     <t>0.663 ± 0.006</t>
   </si>
   <si>
@@ -719,9 +765,15 @@
     <t>0.666 ± 0.005</t>
   </si>
   <si>
+    <t>0.662 ± 0.002</t>
+  </si>
+  <si>
     <t>0.668 ± 0.019</t>
   </si>
   <si>
+    <t>0.665 ± 0.004</t>
+  </si>
+  <si>
     <t>0.669 ± 0.020</t>
   </si>
   <si>
@@ -734,6 +786,9 @@
     <t>0.008 ± 0.010</t>
   </si>
   <si>
+    <t>0.018 ± 0.009</t>
+  </si>
+  <si>
     <t>0.005 ± 0.004</t>
   </si>
   <si>
@@ -749,15 +804,24 @@
     <t>0.015 ± 0.004</t>
   </si>
   <si>
+    <t>0.016 ± 0.000</t>
+  </si>
+  <si>
     <t>0.012 ± 0.005</t>
   </si>
   <si>
+    <t>0.011 ± 0.004</t>
+  </si>
+  <si>
     <t>0.014 ± 0.009</t>
   </si>
   <si>
     <t>0.008 ± 0.006</t>
   </si>
   <si>
+    <t>0.010 ± 0.009</t>
+  </si>
+  <si>
     <t>0.007 ± 0.007</t>
   </si>
   <si>
@@ -776,6 +840,9 @@
     <t>0.003 ± 0.007</t>
   </si>
   <si>
+    <t>0.002 ± 0.004</t>
+  </si>
+  <si>
     <t>0.015 ± 0.007</t>
   </si>
   <si>
@@ -797,15 +864,24 @@
     <t>0.004 ± 0.005</t>
   </si>
   <si>
+    <t>0.005 ± 0.005</t>
+  </si>
+  <si>
     <t>0.004 ± 0.004</t>
   </si>
   <si>
     <t>0.016 ± 0.003</t>
   </si>
   <si>
+    <t>0.018 ± 0.002</t>
+  </si>
+  <si>
     <t>0.007 ± 0.008</t>
   </si>
   <si>
+    <t>0.015 ± 0.002</t>
+  </si>
+  <si>
     <t>0.011 ± 0.010</t>
   </si>
   <si>
@@ -833,12 +909,18 @@
     <t>Reweighing</t>
   </si>
   <si>
+    <t>SMOTE</t>
+  </si>
+  <si>
     <t>Exp. Gradient</t>
   </si>
   <si>
     <t>Threshold Opt.</t>
   </si>
   <si>
+    <t>Reject Option</t>
+  </si>
+  <si>
     <t>RW + TO (hybrid)</t>
   </si>
   <si>
@@ -848,6 +930,9 @@
     <t>[-0.042, 0.000]</t>
   </si>
   <si>
+    <t>[-0.026, 0.000]</t>
+  </si>
+  <si>
     <t>[0.000, 0.000]</t>
   </si>
   <si>
@@ -863,6 +948,9 @@
     <t>[0.000, 0.011]</t>
   </si>
   <si>
+    <t>[0.000, 0.006]</t>
+  </si>
+  <si>
     <t>[-0.011, 0.000]</t>
   </si>
   <si>
@@ -893,9 +981,6 @@
     <t>Accuracy-driven selection</t>
   </si>
   <si>
-    <t>0.994 ± 0.002</t>
-  </si>
-  <si>
     <t>0.993 ± 0.004</t>
   </si>
   <si>
@@ -921,6 +1006,12 @@
   </si>
   <si>
     <t>Overall</t>
+  </si>
+  <si>
+    <t>Mean top-5 overlap (of 5)</t>
+  </si>
+  <si>
+    <t>Mean LIME local R2</t>
   </si>
 </sst>
 </file>
@@ -1331,7 +1422,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -1383,31 +1474,31 @@
         <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E2" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="F2" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="G2" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="H2" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="I2" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="J2" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="K2" t="s">
         <v>154</v>
       </c>
       <c r="L2" t="s">
-        <v>252</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1418,31 +1509,31 @@
         <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E3" t="s">
         <v>95</v>
       </c>
       <c r="F3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="G3" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="H3" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="I3" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="J3" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="K3" t="s">
         <v>154</v>
       </c>
       <c r="L3" t="s">
-        <v>253</v>
+        <v>275</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1453,31 +1544,31 @@
         <v>113</v>
       </c>
       <c r="D4" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E4" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="F4" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="G4" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="H4" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="I4" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="J4" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="K4" t="s">
         <v>154</v>
       </c>
       <c r="L4" t="s">
-        <v>254</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1485,34 +1576,34 @@
         <v>188</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>193</v>
       </c>
       <c r="D5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E5" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="F5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G5" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="H5" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="I5" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="J5" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="K5" t="s">
         <v>154</v>
       </c>
       <c r="L5" t="s">
-        <v>252</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1520,34 +1611,34 @@
         <v>189</v>
       </c>
       <c r="C6" t="s">
-        <v>191</v>
+        <v>107</v>
       </c>
       <c r="D6" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E6" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F6" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="G6" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="H6" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="I6" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="J6" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="K6" t="s">
-        <v>247</v>
+        <v>154</v>
       </c>
       <c r="L6" t="s">
-        <v>161</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1555,174 +1646,174 @@
         <v>190</v>
       </c>
       <c r="C7" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D7" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E7" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="F7" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="G7" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="H7" t="s">
+        <v>238</v>
+      </c>
+      <c r="I7" t="s">
+        <v>252</v>
+      </c>
+      <c r="J7" t="s">
+        <v>261</v>
+      </c>
+      <c r="K7" t="s">
+        <v>268</v>
+      </c>
+      <c r="L7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="B8" t="s">
+        <v>191</v>
+      </c>
+      <c r="C8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" t="s">
+        <v>212</v>
+      </c>
+      <c r="F8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G8" t="s">
         <v>225</v>
       </c>
-      <c r="I7" t="s">
-        <v>235</v>
-      </c>
-      <c r="J7" t="s">
-        <v>242</v>
-      </c>
-      <c r="K7" t="s">
-        <v>247</v>
-      </c>
-      <c r="L7" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" t="s">
-        <v>88</v>
-      </c>
-      <c r="B8" t="s">
-        <v>185</v>
-      </c>
-      <c r="C8" t="s">
-        <v>116</v>
-      </c>
-      <c r="D8" t="s">
-        <v>199</v>
-      </c>
-      <c r="E8" t="s">
-        <v>206</v>
-      </c>
-      <c r="F8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G8" t="s">
-        <v>216</v>
-      </c>
       <c r="H8" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="I8" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="J8" t="s">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="K8" t="s">
-        <v>156</v>
+        <v>269</v>
       </c>
       <c r="L8" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="B9" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>195</v>
       </c>
       <c r="D9" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E9" t="s">
-        <v>98</v>
+        <v>195</v>
       </c>
       <c r="F9" t="s">
+        <v>195</v>
+      </c>
+      <c r="G9" t="s">
+        <v>226</v>
+      </c>
+      <c r="H9" t="s">
+        <v>240</v>
+      </c>
+      <c r="I9" t="s">
+        <v>253</v>
+      </c>
+      <c r="J9" t="s">
+        <v>263</v>
+      </c>
+      <c r="K9" t="s">
+        <v>268</v>
+      </c>
+      <c r="L9" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D10" t="s">
+        <v>204</v>
+      </c>
+      <c r="E10" t="s">
+        <v>213</v>
+      </c>
+      <c r="F10" t="s">
         <v>91</v>
       </c>
-      <c r="G9" t="s">
-        <v>217</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="G10" t="s">
         <v>227</v>
       </c>
-      <c r="I9" t="s">
-        <v>237</v>
-      </c>
-      <c r="J9" t="s">
-        <v>243</v>
-      </c>
-      <c r="K9" t="s">
-        <v>248</v>
-      </c>
-      <c r="L9" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="B10" t="s">
-        <v>187</v>
-      </c>
-      <c r="C10" t="s">
-        <v>193</v>
-      </c>
-      <c r="D10" t="s">
-        <v>119</v>
-      </c>
-      <c r="E10" t="s">
-        <v>206</v>
-      </c>
-      <c r="F10" t="s">
-        <v>98</v>
-      </c>
-      <c r="G10" t="s">
-        <v>218</v>
-      </c>
       <c r="H10" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="I10" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="J10" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="K10" t="s">
-        <v>249</v>
+        <v>156</v>
       </c>
       <c r="L10" t="s">
-        <v>243</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="B11" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C11" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="E11" t="s">
-        <v>206</v>
+        <v>98</v>
       </c>
       <c r="F11" t="s">
         <v>91</v>
       </c>
       <c r="G11" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="H11" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="I11" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="J11" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="K11" t="s">
-        <v>156</v>
+        <v>270</v>
       </c>
       <c r="L11" t="s">
         <v>256</v>
@@ -1730,78 +1821,218 @@
     </row>
     <row r="12" spans="1:12">
       <c r="B12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C12" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D12" t="s">
-        <v>201</v>
+        <v>119</v>
       </c>
       <c r="E12" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="F12" t="s">
-        <v>209</v>
+        <v>98</v>
       </c>
       <c r="G12" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="H12" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="I12" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="J12" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="K12" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="L12" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="B13" t="s">
+        <v>188</v>
+      </c>
+      <c r="C13" t="s">
+        <v>197</v>
+      </c>
+      <c r="D13" t="s">
+        <v>196</v>
+      </c>
+      <c r="E13" t="s">
+        <v>214</v>
+      </c>
+      <c r="F13" t="s">
+        <v>199</v>
+      </c>
+      <c r="G13" t="s">
+        <v>230</v>
+      </c>
+      <c r="H13" t="s">
+        <v>244</v>
+      </c>
+      <c r="I13" t="s">
+        <v>257</v>
+      </c>
+      <c r="J13" t="s">
+        <v>264</v>
+      </c>
+      <c r="K13" t="s">
+        <v>156</v>
+      </c>
+      <c r="L13" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="B14" t="s">
+        <v>189</v>
+      </c>
+      <c r="C14" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14" t="s">
+        <v>204</v>
+      </c>
+      <c r="E14" t="s">
+        <v>213</v>
+      </c>
+      <c r="F14" t="s">
+        <v>91</v>
+      </c>
+      <c r="G14" t="s">
+        <v>227</v>
+      </c>
+      <c r="H14" t="s">
+        <v>241</v>
+      </c>
+      <c r="I14" t="s">
+        <v>254</v>
+      </c>
+      <c r="J14" t="s">
+        <v>264</v>
+      </c>
+      <c r="K14" t="s">
+        <v>156</v>
+      </c>
+      <c r="L14" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="B15" t="s">
         <v>190</v>
       </c>
-      <c r="C13" t="s">
-        <v>195</v>
-      </c>
-      <c r="D13" t="s">
-        <v>202</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="C15" t="s">
+        <v>198</v>
+      </c>
+      <c r="D15" t="s">
+        <v>206</v>
+      </c>
+      <c r="E15" t="s">
+        <v>215</v>
+      </c>
+      <c r="F15" t="s">
+        <v>218</v>
+      </c>
+      <c r="G15" t="s">
+        <v>231</v>
+      </c>
+      <c r="H15" t="s">
+        <v>245</v>
+      </c>
+      <c r="I15" t="s">
+        <v>258</v>
+      </c>
+      <c r="J15" t="s">
+        <v>266</v>
+      </c>
+      <c r="K15" t="s">
+        <v>272</v>
+      </c>
+      <c r="L15" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="B16" t="s">
+        <v>191</v>
+      </c>
+      <c r="C16" t="s">
+        <v>199</v>
+      </c>
+      <c r="D16" t="s">
+        <v>207</v>
+      </c>
+      <c r="E16" t="s">
+        <v>216</v>
+      </c>
+      <c r="F16" t="s">
+        <v>109</v>
+      </c>
+      <c r="G16" t="s">
+        <v>232</v>
+      </c>
+      <c r="H16" t="s">
+        <v>246</v>
+      </c>
+      <c r="I16" t="s">
+        <v>259</v>
+      </c>
+      <c r="J16" t="s">
+        <v>264</v>
+      </c>
+      <c r="K16" t="s">
+        <v>164</v>
+      </c>
+      <c r="L16" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12">
+      <c r="B17" t="s">
+        <v>192</v>
+      </c>
+      <c r="C17" t="s">
+        <v>200</v>
+      </c>
+      <c r="D17" t="s">
         <v>208</v>
       </c>
-      <c r="F13" t="s">
-        <v>210</v>
-      </c>
-      <c r="G13" t="s">
-        <v>220</v>
-      </c>
-      <c r="H13" t="s">
-        <v>230</v>
-      </c>
-      <c r="I13" t="s">
-        <v>240</v>
-      </c>
-      <c r="J13" t="s">
-        <v>246</v>
-      </c>
-      <c r="K13" t="s">
-        <v>251</v>
-      </c>
-      <c r="L13" t="s">
-        <v>258</v>
+      <c r="E17" t="s">
+        <v>217</v>
+      </c>
+      <c r="F17" t="s">
+        <v>219</v>
+      </c>
+      <c r="G17" t="s">
+        <v>233</v>
+      </c>
+      <c r="H17" t="s">
+        <v>247</v>
+      </c>
+      <c r="I17" t="s">
+        <v>260</v>
+      </c>
+      <c r="J17" t="s">
+        <v>267</v>
+      </c>
+      <c r="K17" t="s">
+        <v>273</v>
+      </c>
+      <c r="L17" t="s">
+        <v>283</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="A10:A17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1809,7 +2040,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1897,7 +2128,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.984</v>
+        <v>0.982</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1908,16 +2139,16 @@
         <v>189</v>
       </c>
       <c r="C6">
-        <v>0.997</v>
+        <v>1</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0.992</v>
+        <v>0.984</v>
       </c>
       <c r="F6">
-        <v>0.003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1925,41 +2156,38 @@
         <v>190</v>
       </c>
       <c r="C7">
-        <v>0.998</v>
+        <v>0.997</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0.998</v>
+        <v>0.992</v>
       </c>
       <c r="F7">
         <v>0.003</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" t="s">
-        <v>88</v>
-      </c>
       <c r="B8" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0.998</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0.987</v>
+        <v>0.99</v>
       </c>
       <c r="F8">
-        <v>0.019</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="B9" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C9">
         <v>0.998</v>
@@ -1968,15 +2196,18 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0.984</v>
+        <v>0.998</v>
       </c>
       <c r="F9">
-        <v>0.016</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>88</v>
+      </c>
       <c r="B10" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1985,67 +2216,135 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0.985</v>
+        <v>0.987</v>
       </c>
       <c r="F10">
-        <v>0.024</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="B11" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>0.998</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0.987</v>
+        <v>0.984</v>
       </c>
       <c r="F11">
-        <v>0.019</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="B12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C12">
-        <v>0.976</v>
+        <v>1</v>
       </c>
       <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0.985</v>
+      </c>
+      <c r="F12">
         <v>0.024</v>
-      </c>
-      <c r="E12">
-        <v>0.979</v>
-      </c>
-      <c r="F12">
-        <v>0.016</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="B13" t="s">
+        <v>188</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0.984</v>
+      </c>
+      <c r="F13">
+        <v>0.019</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="B14" t="s">
+        <v>189</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0.987</v>
+      </c>
+      <c r="F14">
+        <v>0.019</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="B15" t="s">
         <v>190</v>
       </c>
-      <c r="C13">
+      <c r="C15">
+        <v>0.976</v>
+      </c>
+      <c r="D15">
+        <v>0.024</v>
+      </c>
+      <c r="E15">
+        <v>0.979</v>
+      </c>
+      <c r="F15">
+        <v>0.016</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="B16" t="s">
+        <v>191</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0.989</v>
+      </c>
+      <c r="F16">
+        <v>0.019</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" t="s">
+        <v>192</v>
+      </c>
+      <c r="C17">
         <v>0.973</v>
       </c>
-      <c r="D13">
+      <c r="D17">
         <v>0.03</v>
       </c>
-      <c r="E13">
+      <c r="E17">
         <v>0.977</v>
       </c>
-      <c r="F13">
+      <c r="F17">
         <v>0.016</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="A10:A17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2053,7 +2352,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2064,22 +2363,22 @@
         <v>184</v>
       </c>
       <c r="D1" t="s">
-        <v>259</v>
+        <v>284</v>
       </c>
       <c r="E1" t="s">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="F1" t="s">
-        <v>261</v>
+        <v>286</v>
       </c>
       <c r="G1" t="s">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="H1" t="s">
-        <v>263</v>
+        <v>288</v>
       </c>
       <c r="I1" t="s">
-        <v>264</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2090,13 +2389,13 @@
         <v>82</v>
       </c>
       <c r="C2" t="s">
-        <v>265</v>
+        <v>290</v>
       </c>
       <c r="D2">
         <v>0.008</v>
       </c>
       <c r="E2" t="s">
-        <v>270</v>
+        <v>297</v>
       </c>
       <c r="F2">
         <v>0.742</v>
@@ -2105,7 +2404,7 @@
         <v>-0.002</v>
       </c>
       <c r="H2" t="s">
-        <v>275</v>
+        <v>303</v>
       </c>
       <c r="I2">
         <v>0.742</v>
@@ -2119,13 +2418,13 @@
         <v>82</v>
       </c>
       <c r="C3" t="s">
-        <v>266</v>
+        <v>291</v>
       </c>
       <c r="D3">
         <v>-0.016</v>
       </c>
       <c r="E3" t="s">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="F3">
         <v>0.264</v>
@@ -2134,7 +2433,7 @@
         <v>0.004</v>
       </c>
       <c r="H3" t="s">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="I3">
         <v>0.264</v>
@@ -2148,25 +2447,25 @@
         <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>-0.008</v>
       </c>
       <c r="E4" t="s">
-        <v>272</v>
+        <v>299</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0.704</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="H4" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0.704</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2177,25 +2476,25 @@
         <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>268</v>
+        <v>293</v>
       </c>
       <c r="D5">
-        <v>-0.016</v>
+        <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>271</v>
+        <v>300</v>
       </c>
       <c r="F5">
-        <v>0.264</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>276</v>
+        <v>300</v>
       </c>
       <c r="I5">
-        <v>0.264</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2206,13 +2505,13 @@
         <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>269</v>
+        <v>294</v>
       </c>
       <c r="D6">
         <v>-0.016</v>
       </c>
       <c r="E6" t="s">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="F6">
         <v>0.264</v>
@@ -2221,7 +2520,7 @@
         <v>0.004</v>
       </c>
       <c r="H6" t="s">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="I6">
         <v>0.264</v>
@@ -2232,28 +2531,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>265</v>
+        <v>295</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>-0.016</v>
       </c>
       <c r="E7" t="s">
-        <v>272</v>
+        <v>298</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>0.264</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="H7" t="s">
-        <v>272</v>
+        <v>304</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0.264</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2261,28 +2560,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="D8">
-        <v>0.006</v>
+        <v>-0.016</v>
       </c>
       <c r="E8" t="s">
-        <v>270</v>
+        <v>298</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0.264</v>
       </c>
       <c r="G8">
-        <v>-0.003</v>
+        <v>0.004</v>
       </c>
       <c r="H8" t="s">
-        <v>277</v>
+        <v>304</v>
       </c>
       <c r="I8">
-        <v>0.792</v>
+        <v>0.264</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2293,13 +2592,13 @@
         <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>267</v>
+        <v>290</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -2308,7 +2607,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -2322,25 +2621,25 @@
         <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="D10">
-        <v>0.028</v>
+        <v>0.006</v>
       </c>
       <c r="E10" t="s">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="F10">
-        <v>0.632</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>-0.006</v>
+        <v>-0.003</v>
       </c>
       <c r="H10" t="s">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="I10">
-        <v>0.494</v>
+        <v>0.792</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2351,24 +2650,140 @@
         <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>300</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
+        <v>300</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" t="s">
+        <v>293</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12" t="s">
+        <v>300</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
+        <v>300</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" t="s">
+        <v>294</v>
+      </c>
+      <c r="D13">
+        <v>0.028</v>
+      </c>
+      <c r="E13" t="s">
+        <v>301</v>
+      </c>
+      <c r="F13">
+        <v>0.632</v>
+      </c>
+      <c r="G13">
+        <v>-0.006</v>
+      </c>
+      <c r="H13" t="s">
+        <v>307</v>
+      </c>
+      <c r="I13">
+        <v>0.494</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" t="s">
+        <v>295</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>300</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14" t="s">
+        <v>300</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" t="s">
+        <v>296</v>
+      </c>
+      <c r="D15">
         <v>0.052</v>
       </c>
-      <c r="E11" t="s">
-        <v>274</v>
-      </c>
-      <c r="F11">
+      <c r="E15" t="s">
+        <v>302</v>
+      </c>
+      <c r="F15">
         <v>0.372</v>
       </c>
-      <c r="G11">
+      <c r="G15">
         <v>-0.01</v>
       </c>
-      <c r="H11" t="s">
-        <v>279</v>
-      </c>
-      <c r="I11">
+      <c r="H15" t="s">
+        <v>308</v>
+      </c>
+      <c r="I15">
         <v>0.108</v>
       </c>
     </row>
@@ -2384,13 +2799,13 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" t="s">
-        <v>280</v>
+        <v>309</v>
       </c>
       <c r="C1" t="s">
-        <v>281</v>
+        <v>310</v>
       </c>
       <c r="D1" t="s">
-        <v>282</v>
+        <v>311</v>
       </c>
       <c r="E1" t="s">
         <v>175</v>
@@ -2399,10 +2814,10 @@
         <v>184</v>
       </c>
       <c r="G1" t="s">
-        <v>283</v>
+        <v>312</v>
       </c>
       <c r="H1" t="s">
-        <v>284</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -2416,7 +2831,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="E2" t="s">
         <v>82</v>
@@ -2442,7 +2857,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>286</v>
+        <v>315</v>
       </c>
       <c r="E3" t="s">
         <v>82</v>
@@ -2468,16 +2883,16 @@
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="E4" t="s">
         <v>82</v>
       </c>
       <c r="F4" t="s">
-        <v>268</v>
+        <v>295</v>
       </c>
       <c r="G4">
-        <v>0.991</v>
+        <v>0.993</v>
       </c>
       <c r="H4">
         <v>0.011</v>
@@ -2494,7 +2909,7 @@
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>286</v>
+        <v>315</v>
       </c>
       <c r="E5" t="s">
         <v>82</v>
@@ -2520,13 +2935,13 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="E6" t="s">
         <v>82</v>
       </c>
       <c r="F6" t="s">
-        <v>266</v>
+        <v>291</v>
       </c>
       <c r="G6">
         <v>0.997</v>
@@ -2546,7 +2961,7 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>286</v>
+        <v>315</v>
       </c>
       <c r="E7" t="s">
         <v>82</v>
@@ -2572,13 +2987,13 @@
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="E8" t="s">
         <v>82</v>
       </c>
       <c r="F8" t="s">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -2598,7 +3013,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>286</v>
+        <v>315</v>
       </c>
       <c r="E9" t="s">
         <v>82</v>
@@ -2624,13 +3039,13 @@
         <v>5</v>
       </c>
       <c r="D10" t="s">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="E10" t="s">
         <v>82</v>
       </c>
       <c r="F10" t="s">
-        <v>265</v>
+        <v>290</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -2650,7 +3065,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>286</v>
+        <v>315</v>
       </c>
       <c r="E11" t="s">
         <v>82</v>
@@ -2676,13 +3091,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="E12" t="s">
         <v>88</v>
       </c>
       <c r="F12" t="s">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="G12">
         <v>0.972</v>
@@ -2702,7 +3117,7 @@
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>286</v>
+        <v>315</v>
       </c>
       <c r="E13" t="s">
         <v>82</v>
@@ -2728,13 +3143,13 @@
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="E14" t="s">
         <v>82</v>
       </c>
       <c r="F14" t="s">
-        <v>266</v>
+        <v>291</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -2754,7 +3169,7 @@
         <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>286</v>
+        <v>315</v>
       </c>
       <c r="E15" t="s">
         <v>82</v>
@@ -2780,13 +3195,13 @@
         <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="E16" t="s">
         <v>82</v>
       </c>
       <c r="F16" t="s">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="G16">
         <v>0.987</v>
@@ -2806,7 +3221,7 @@
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>286</v>
+        <v>315</v>
       </c>
       <c r="E17" t="s">
         <v>82</v>
@@ -2832,13 +3247,13 @@
         <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="E18" t="s">
         <v>82</v>
       </c>
       <c r="F18" t="s">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="G18">
         <v>0.992</v>
@@ -2858,7 +3273,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="s">
-        <v>286</v>
+        <v>315</v>
       </c>
       <c r="E19" t="s">
         <v>82</v>
@@ -2884,7 +3299,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="s">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="E20" t="s">
         <v>82</v>
@@ -2910,7 +3325,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="s">
-        <v>286</v>
+        <v>315</v>
       </c>
       <c r="E21" t="s">
         <v>82</v>
@@ -2937,7 +3352,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>282</v>
+        <v>311</v>
       </c>
       <c r="B1" t="s">
         <v>76</v>
@@ -2960,48 +3375,48 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="B2" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C2" t="s">
-        <v>288</v>
+        <v>316</v>
       </c>
       <c r="D2" t="s">
         <v>99</v>
       </c>
       <c r="E2" t="s">
-        <v>290</v>
+        <v>318</v>
       </c>
       <c r="F2" t="s">
-        <v>290</v>
+        <v>318</v>
       </c>
       <c r="G2" t="s">
-        <v>292</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>286</v>
+        <v>315</v>
       </c>
       <c r="B3" t="s">
-        <v>287</v>
+        <v>216</v>
       </c>
       <c r="C3" t="s">
-        <v>289</v>
+        <v>317</v>
       </c>
       <c r="D3" t="s">
         <v>99</v>
       </c>
       <c r="E3" t="s">
-        <v>291</v>
+        <v>319</v>
       </c>
       <c r="F3" t="s">
-        <v>291</v>
+        <v>319</v>
       </c>
       <c r="G3" t="s">
-        <v>293</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -3011,7 +3426,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -3022,7 +3437,7 @@
         <v>184</v>
       </c>
       <c r="D1" t="s">
-        <v>294</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -3047,10 +3462,10 @@
         <v>82</v>
       </c>
       <c r="C3" t="s">
-        <v>266</v>
+        <v>295</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3061,10 +3476,10 @@
         <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3075,10 +3490,10 @@
         <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -3086,12 +3501,26 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" t="s">
+        <v>290</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
         <v>88</v>
       </c>
-      <c r="C6" t="s">
-        <v>268</v>
-      </c>
-      <c r="D6">
+      <c r="C7" t="s">
+        <v>294</v>
+      </c>
+      <c r="D7">
         <v>1</v>
       </c>
     </row>
@@ -3102,7 +3531,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -3119,7 +3548,7 @@
         <v>123</v>
       </c>
       <c r="E1" t="s">
-        <v>295</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3172,10 +3601,10 @@
         <v>188</v>
       </c>
       <c r="C5">
-        <v>0.996</v>
+        <v>0.995</v>
       </c>
       <c r="D5">
-        <v>0.016</v>
+        <v>0.018</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -3189,7 +3618,7 @@
         <v>0.996</v>
       </c>
       <c r="D6">
-        <v>0.008</v>
+        <v>0.016</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -3200,27 +3629,24 @@
         <v>190</v>
       </c>
       <c r="C7">
-        <v>0.998</v>
+        <v>0.996</v>
       </c>
       <c r="D7">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="E7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>88</v>
-      </c>
       <c r="B8" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="C8">
-        <v>0.989</v>
+        <v>0.996</v>
       </c>
       <c r="D8">
-        <v>0.019</v>
+        <v>0.01</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -3228,27 +3654,30 @@
     </row>
     <row r="9" spans="1:5">
       <c r="B9" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C9">
+        <v>0.998</v>
+      </c>
+      <c r="D9">
+        <v>0.007</v>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C10">
         <v>0.989</v>
       </c>
-      <c r="D9">
+      <c r="D10">
         <v>0.019</v>
-      </c>
-      <c r="E9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="B10" t="s">
-        <v>187</v>
-      </c>
-      <c r="C10">
-        <v>0.987</v>
-      </c>
-      <c r="D10">
-        <v>0.024</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -3256,7 +3685,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="B11" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C11">
         <v>0.989</v>
@@ -3270,13 +3699,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="B12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C12">
-        <v>0.98</v>
+        <v>0.987</v>
       </c>
       <c r="D12">
-        <v>0.031</v>
+        <v>0.024</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -3284,22 +3713,78 @@
     </row>
     <row r="13" spans="1:5">
       <c r="B13" t="s">
+        <v>188</v>
+      </c>
+      <c r="C13">
+        <v>0.988</v>
+      </c>
+      <c r="D13">
+        <v>0.019</v>
+      </c>
+      <c r="E13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="B14" t="s">
+        <v>189</v>
+      </c>
+      <c r="C14">
+        <v>0.989</v>
+      </c>
+      <c r="D14">
+        <v>0.019</v>
+      </c>
+      <c r="E14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="B15" t="s">
         <v>190</v>
       </c>
-      <c r="C13">
+      <c r="C15">
+        <v>0.98</v>
+      </c>
+      <c r="D15">
+        <v>0.031</v>
+      </c>
+      <c r="E15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="B16" t="s">
+        <v>191</v>
+      </c>
+      <c r="C16">
+        <v>0.99</v>
+      </c>
+      <c r="D16">
+        <v>0.019</v>
+      </c>
+      <c r="E16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17" t="s">
+        <v>192</v>
+      </c>
+      <c r="C17">
         <v>0.978</v>
       </c>
-      <c r="D13">
+      <c r="D17">
         <v>0.036</v>
       </c>
-      <c r="E13" t="b">
+      <c r="E17" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="A10:A17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3318,7 +3803,7 @@
         <v>20</v>
       </c>
       <c r="D1" t="s">
-        <v>296</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -3655,6 +4140,72 @@
       </c>
       <c r="D25">
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2">
+        <v>25</v>
+      </c>
+      <c r="C2">
+        <v>2.84</v>
+      </c>
+      <c r="D2">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3">
+        <v>25</v>
+      </c>
+      <c r="C3">
+        <v>3.56</v>
+      </c>
+      <c r="D3">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4">
+        <v>50</v>
+      </c>
+      <c r="C4">
+        <v>3.2</v>
+      </c>
+      <c r="D4">
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>
